--- a/public/assets/excel/rawan_bencana.xlsx
+++ b/public/assets/excel/rawan_bencana.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/MyApp/Laravel/app_sipkawan_dprkp/public/assets/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2FCFC6-09F5-7E41-8765-E5AC83F31BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3FC963-5051-4E41-92BA-328F9C056F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19340" xr2:uid="{7B27874A-EF13-6240-B57F-BD08AB24D295}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,15 +61,6 @@
     <t>Jumlah Jiwa</t>
   </si>
   <si>
-    <t>Kondisi Rumah</t>
-  </si>
-  <si>
-    <t>Status Kepemilikan Rumah</t>
-  </si>
-  <si>
-    <t>RLH</t>
-  </si>
-  <si>
     <t>Tahun</t>
   </si>
   <si>
@@ -82,9 +73,6 @@
     <t>Sungai Jingah</t>
   </si>
   <si>
-    <t>Hak Milik</t>
-  </si>
-  <si>
     <t>RW</t>
   </si>
   <si>
@@ -92,6 +80,18 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Status Kepemilikan (Hak Milik)</t>
+  </si>
+  <si>
+    <t>Status Kepemilikan (Sewa)</t>
+  </si>
+  <si>
+    <t>Kondisi Rumah (RTLH)</t>
+  </si>
+  <si>
+    <t>Kondisi Rumah (RLH)</t>
   </si>
 </sst>
 </file>
@@ -128,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -188,11 +188,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -209,6 +271,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1516B71B-CF8E-9449-ABEE-9967DA680D54}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
@@ -538,11 +606,12 @@
     <col min="10" max="10" width="15.1640625" customWidth="1"/>
     <col min="11" max="11" width="18.5" customWidth="1"/>
     <col min="12" max="12" width="18.1640625" customWidth="1"/>
+    <col min="13" max="14" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -557,10 +626,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>4</v>
@@ -575,13 +644,19 @@
         <v>7</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>2022</v>
       </c>
@@ -589,19 +664,19 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H2" s="4">
         <v>123</v>
@@ -615,14 +690,20 @@
       <c r="K2" s="4">
         <v>123</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L2" s="4">
+        <v>123</v>
+      </c>
+      <c r="M2" s="4">
+        <v>123</v>
+      </c>
+      <c r="N2" s="8">
+        <v>123</v>
+      </c>
+      <c r="O2" s="9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -636,8 +717,10 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N3" s="10"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -651,8 +734,10 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N4" s="10"/>
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -666,8 +751,10 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5" s="10"/>
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -681,8 +768,10 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N6" s="10"/>
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -696,8 +785,10 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="10"/>
+      <c r="O7" s="11"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -711,8 +802,10 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="10"/>
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -726,8 +819,10 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="10"/>
+      <c r="O9" s="11"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -741,8 +836,10 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="10"/>
+      <c r="O10" s="11"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -756,8 +853,10 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="10"/>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -771,6 +870,8 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
